--- a/04_DESIGN_TABLES/DesignTable_6565_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6565_SW2.xlsx
@@ -1645,7 +1645,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>Air-Way s104 only (double-pass 9 rows); C3_1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2057 Nut Hex 1 = 1.000 (table had 0.94); C3_2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!Y2057 Nut Hex 2 = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: BOTH ends female JIC swivel; L31 = nut face to nut face, L32 = seat to seat, (L31-L32)/2 taken as the nut-face-to-seat length of each end (all built rows have equal dashes, so the split is symmetric); body hex C between the two body faces, nut hexes C3(1)/C3(2) (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex runs between the two measured body-face positions (6500 forged-arm end, ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1/D2 stepped at the body-hex mid-plane (ASSUMPTION, as 2403); both swivel seats: the 37deg seat cone ends at the through-bore (D1 at End A, D2 at End B) with no flat, as measured on the Brennan 6500-04..-32-FG swivel legs (all 10 sizes, 2026-10-01) and as drawn in the Brennan TFA catalog p.18 for 6565 (no Brennan 6565 STEP - ASSUMED for the double swivel); the DRIVE sketch draws each seat cone down to the bore radius (SWA_SEATENDR / SWB_SEATENDR = D1/2 / D2/2) and closes it radially to the axis; the bore cuts remove the core between the two seats</t>
+          <t>[BRENNAN-CELL 2026-10-20: C3_2HEX@HEX] [BRENNAN-CELL 2026-10-20: C3_1HEX@HEX] Air-Way s104 only (double-pass 9 rows); C3_1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2057 Nut Hex 1 = 1.000 (table had 0.94); C3_2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!Y2057 Nut Hex 2 = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C3_1HEX@HEX: Brennan TFA catalog p18 table TFA-p018-t04 "FJS-FJS STRAIGHT" row 6565-10-10 col "C1 HEX" = 1.000 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan]; C3_2HEX@HEX: Brennan TFA catalog p18 table TFA-p018-t04 "FJS-FJS STRAIGHT" row 6565-10-10 col "C2 HEX" = 1.000 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan] | MODEL: BOTH ends female JIC swivel; L31 = nut face to nut face, L32 = seat to seat, (L31-L32)/2 taken as the nut-face-to-seat length of each end (all built rows have equal dashes, so the split is symmetric); body hex C between the two body faces, nut hexes C3(1)/C3(2) (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex runs between the two measured body-face positions (6500 forged-arm end, ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore D1/D2 stepped at the body-hex mid-plane (ASSUMPTION, as 2403); both swivel seats: the 37deg seat cone ends at the through-bore (D1 at End A, D2 at End B) with no flat, as measured on the Brennan 6500-04..-32-FG swivel legs (all 10 sizes, 2026-10-01) and as drawn in the Brennan TFA catalog p.18 for 6565 (no Brennan 6565 STEP - ASSUMED for the double swivel); the DRIVE sketch draws each seat cone down to the bore radius (SWA_SEATENDR / SWB_SEATENDR = D1/2 / D2/2) and closes it radially to the axis; the bore cuts remove the core between the two seats</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>2026-10-20 C3_1HEX@HEX = Brennan 1 (Air-Way 0.94 cannot be built: Air-Way nut hex 0.94 vs the Brennan -10 swivel nut (1.000) the nut shape is measured from (generator: no end data)) | 2026-10-20 C3_2HEX@HEX = Brennan 1 (Air-Way 0.94 cannot be built: Air-Way nut hex 0.94 vs the Brennan -10 swivel nut (1.000) the nut shape is measured from (generator: no end data))</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
